--- a/Test Cases/Signup_Test_Cases.xlsx
+++ b/Test Cases/Signup_Test_Cases.xlsx
@@ -2,22 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14380" windowHeight="4410" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Signup Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,23 +25,59 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -55,17 +90,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -428,1394 +474,1251 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="41" customWidth="1" min="6" max="6"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TC ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>TICHI WEB APPLICATION - SIGNUP TEST CASES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Tichi Web Application</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Signup</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Document Name</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Signup Test Cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Application URL</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>https://tichi-app-webapp-stage.web.app</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Prepared By</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Sudharsan D</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Execution Date</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>02-Jul-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="29" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Test Case Name</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Test Type</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TC_SIGNUP_001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Signup</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Verify Signup page loads</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Application URL</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Open Signup page</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Signup page displayed</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TC_SIGNUP_002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Signup</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Verify First Name field</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Signup page</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Observe field</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Field displayed</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TC_SIGNUP_003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Signup</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Verify Last Name field</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Signup page</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Observe field</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Field displayed</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TC_SIGNUP_004</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Signup</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Verify Mobile Number field</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Signup page</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Observe field</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Field displayed</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TC_SIGNUP_005</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Signup</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Verify Email field</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Signup page</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Observe field</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Field displayed</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TC_SIGNUP_006</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Signup</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Verify Password field</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Signup page</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Observe field</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Field displayed</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TC_SIGNUP_007</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Signup</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Verify Confirm Password field</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Signup page</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Observe field</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Field displayed</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_008</t>
+          <t>SIGNUP_001</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify Signup page loads successfully</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Verify successful signup</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Mandatory fields available</t>
+          <t>Signup</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Fill form and submit</t>
+          <t>Application accessible</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Valid user details</t>
+          <t>1.Open Signup page</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Verification page displayed</t>
+          <t>Signup page should load successfully</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
+          <t>Signup page loaded with all mandatory fields.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_009</t>
+          <t>SIGNUP_002</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify First Name field</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Verify First Name mandatory</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Signup page</t>
+          <t>Signup</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Leave First Name blank</t>
+          <t>Signup page opened</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Blank</t>
+          <t>1.Enter first name</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Validation displayed</t>
+          <t>Field should accept valid input</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
+          <t>Accepted valid first name.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_010</t>
+          <t>SIGNUP_003</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify Last Name field</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Verify Email mandatory</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>Signup</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Signup page opened</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1.Enter last name</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Field should accept valid input</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Accepted valid last name.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="29" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SIGNUP_004</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Verify Mobile accepts numbers only</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Signup</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>Signup page</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Leave Email blank</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Blank</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Validation displayed</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TC_SIGNUP_011</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Signup</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Verify Password mandatory</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Signup page</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Leave Password blank</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Blank</t>
+          <t>1.Try alphabets</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Validation displayed</t>
+          <t>Only digits should be accepted</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
+          <t>Alphabetic characters were not accepted.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Input restriction works.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_012</t>
+          <t>SIGNUP_005</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify Mobile rejects special characters</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Verify Confirm Password mandatory</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Signup</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>Signup page</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Leave Confirm Password blank</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Blank</t>
+          <t>1.Try special characters</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Validation displayed</t>
+          <t>Special characters should not be accepted</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
+          <t>Special characters were blocked.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="87" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_013</t>
+          <t>SIGNUP_006</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify Mobile maximum length</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Verify invalid email format</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Signup</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>Signup page</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Enter invalid email</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Invalid email format</t>
+          <t>1.Enter more than 10 digits</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Validation displayed</t>
+          <t>Only 10 digits allowed</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
+          <t>Input restricted to 10 digits.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Maximum length enforced.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_014</t>
+          <t>SIGNUP_007</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify Mobile minimum length</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Verify duplicate email</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Existing account</t>
+          <t>Signup</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Register existing email</t>
+          <t>Signup page</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Registered email</t>
+          <t>1.Enter fewer than 10 digits
+2.Submit</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Duplicate email error</t>
+          <t>Submission should be blocked</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
+          <t>Browser requested minimum 10 characters.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Validation displayed correctly.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_015</t>
+          <t>SIGNUP_09</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify Password policy</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Verify mobile number with less than 10 digits</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Signup</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>Signup page</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Enter short mobile</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Mobile number with less than 10 digits</t>
+          <t>1.Focus Password</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Validation message should be displayed when submitting the form.</t>
+          <t>Password rules displayed</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
+          <t>Password policy displayed.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_016</t>
+          <t>SIGNUP_010</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify weak password feedback</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Verify the Mobile Number field accepts only numeric characters</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Signup</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>Signup page</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Enter long mobile</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Alphabetic characters</t>
+          <t>1.Enter weak password</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>The Mobile Number field should not accept alphabetic characters.</t>
+          <t>Missing requirements highlighted</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
+          <t>Real-time feedback displayed.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Validation works.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_017</t>
+          <t>SIGNUP_011</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify strong password</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Verify the Mobile Number field accepts only numeric characters</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Signup</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>Signup page</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Enter alphabets</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Special characters</t>
+          <t>1.Enter strong password</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>The Mobile Number field should not accept special characters.</t>
+          <t>Password accepted</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
+          <t>Strong password accepted.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="29" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_018</t>
+          <t>SIGNUP_012</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify Password visibility</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Verify the Mobile Number field restricts input to a maximum of 10 digits</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>Signup</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>Signup page</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Enter special chars</t>
-        </is>
-      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>More than 10 digits</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>The user should not be able to enter more than 10 digits.</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
+          <t>1.Click eye icon</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Password visibility should toggle when the eye icon is clicked.</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Password visibility toggled successfully when the eye icon was clicked.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Password visibility toggle is working as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="29" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_019</t>
+          <t>SIGNUP_013</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify Confirm Password visibility</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Verify password mismatch</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>Signup</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>Signup page</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Enter different passwords</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Different passwords</t>
+          <t>1.Click eye icon</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Mismatch message</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
+          <t>Visibility toggles</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Password visibility toggled successfully.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="29" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_020</t>
+          <t>SIGNUP_014</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify Password mismatch</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Verify password without uppercase</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>Signup</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>Signup page</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Enter password</t>
-        </is>
-      </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Password without uppercase</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Policy validation</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
+          <t>1.Enter different passwords</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Display a password mismatch validation message.</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>The application displayed: "Confirm password must be match with password".</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Validation functionality works correctly; however, the validation message contains a grammatical error. Recommended message: "Confirm password must match the password." or "Passwords do not match."</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="29" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_021</t>
+          <t>SIGNUP_015</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify Empty Password</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Verify password without lowercase</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>Signup</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>Signup page</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Enter password</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Password without lowercase</t>
+          <t>1.Leave Password blank</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Policy validation</t>
+          <t>Required validation</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
+          <t>Password is required displayed.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_022</t>
+          <t>SIGNUP_016</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify Empty Confirm Password</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Verify password without number</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Signup</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>Signup page</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Enter password</t>
-        </is>
-      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Password without number</t>
+          <t>1.Leave Confirm Password blank</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Policy validation</t>
+          <t>Required validation</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
+          <t>Confirm password is required displayed.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_023</t>
+          <t>SIGNUP_017</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify Terms &amp; Conditions checkbox presence</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Verify password without special character</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Signup</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>Signup page</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Enter password</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Password without special character</t>
+          <t>1.Verify checkbox</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Policy validation</t>
+          <t>Checkbox displayed</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
+          <t>Checkbox displayed.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_024</t>
+          <t>SIGNUP_018</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify Sign Up button</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Verify password &lt;8 chars</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>Signup</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>Signup page</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Enter short password</t>
-        </is>
-      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Less than 8 chars</t>
+          <t>1.Open page</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Policy validation</t>
+          <t>Button visible</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
+          <t>Sign Up button displayed.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_025</t>
+          <t>SIGNUP_019</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify mandatory fields</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Verify password &gt;20 chars</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Signup</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>Signup page</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Enter long password</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>More than 20 chars</t>
+          <t>1.Leave mandatory fields blank
+2.Submit</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Policy validation</t>
+          <t>Required messages displayed</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
+          <t>Mandatory validations displayed.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Working as expected.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_026</t>
+          <t>SIGNUP_020</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify successful signup</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Verify Terms unchecked</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Signup page</t>
+          <t>Signup</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Leave checkbox unchecked</t>
+          <t>Valid unique data</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Unchecked</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Registration blocked</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
+          <t>1.Fill form
+2.Submit</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Account should be created successfully.</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>User account was successfully created and the record was stored in the database.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Account creation verified successfully.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_027</t>
+          <t>SIGNUP_021</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify UI alignment</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Verify password visibility</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Password entered</t>
+          <t>Signup</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Click eye icon</t>
+          <t>Signup page</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Valid password</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Visibility toggles</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
+          <t>1.Open page</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>All UI controls should be properly aligned and displayed without layout issues</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>All UI controls were displayed correctly with proper alignment and spacing.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>No UI alignment or rendering issues observed.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TC_SIGNUP_028</t>
+          <t>SIGNUP_022</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Signup</t>
+          <t>Verify field placeholders</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Verify resend verification</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Verification page</t>
+          <t>Signup</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Click Resend</t>
+          <t>Signup page</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Registered email</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Verification resent</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TC_SIGNUP_029</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Signup</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Verify email verification page</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Signup success</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Complete signup</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Valid user</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Verification page displayed</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TC_SIGNUP_030</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Signup</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Verify responsive UI</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Resize browser</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Observe layout</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Desktop/Mobile</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>UI aligned</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
+          <t>1.Check placeholders</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>All input fields should display clear and meaningful placeholder text.</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Placeholder text was displayed correctly for all applicable input fields.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Placeholder text displayed as expected.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>